--- a/data/trans_camb/IP21B-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>13.24790997563369</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-12.80430011968768</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.240917951233048</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-18.6053963093438</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>9.914006031541383</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-14.92331125767854</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-13.08585729832961</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-32.26770557881409</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-28.6726940506855</v>
+      </c>
       <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>-10.31246423983871</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-30.82242590045157</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +650,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>57.67222163932956</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-3.983404574368286</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>35.84732063382675</v>
+      </c>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>33.46835055036833</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-5.392918642443013</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +674,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>1.034645380989151</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.2816880578136898</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.6643301784944209</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -703,11 +704,10 @@
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.5693182787624113</v>
+      </c>
       <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -720,11 +720,10 @@
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>5.093159727353947</v>
+      </c>
       <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +736,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-19.77639767012328</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-29.23852313383814</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-11.7833145802893</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>15.62124662964145</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-12.03416091209504</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.510287492870516</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +762,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-58.09107960981953</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-60.80107319493882</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-36.2114298771334</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-17.85840257382069</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-29.95401308514526</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-25.3629701413085</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +788,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>9.729389310235188</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-8.919056447626909</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>68.64376571713233</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.555801623884348</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>52.90347479345117</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +814,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.6763815525017333</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.325709037402099</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.6586997486346028</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.08266683478695504</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -809,11 +844,12 @@
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -826,11 +862,12 @@
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>2.663584774559582</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>10.36753656427805</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +880,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>5.41914095538461</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>29.90172851224615</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>14.18246430539529</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>17.34749759592473</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>10.24348474544397</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>24.14925277614596</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +906,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-28.46493627776779</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-16.68209177498795</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-31.33317982962033</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-32.11202334403333</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-18.53130312376866</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-9.507202277512437</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +932,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>44.41878828140099</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>72.68273395243894</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>57.67656713367176</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>67.9950875263811</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>39.4941317864257</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>55.57450630588868</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +958,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.2819499278023598</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1.555742923943784</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.6344533960298462</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.7760413511611706</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.4942373651407623</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.165176046902319</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -916,10 +989,9 @@
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-0.3834736157737182</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -933,10 +1005,9 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>8.768297902615458</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1020,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>13.62327083556927</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-6.430797821064613</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>18.68933357159259</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>10.73152853254413</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.7110467770371054</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1046,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-50.57031624903922</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-57.70125603247806</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="n">
+        <v>-31.23536374670556</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-44.97748224978807</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1070,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>74.92668122961726</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>45.51475445670073</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>66.24072108425571</v>
+      </c>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="n">
+        <v>47.41441973094718</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>33.02104553613064</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1094,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.5395010589572792</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2546688145805732</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
       <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="n">
+        <v>0.7206994947098539</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.04775191636230267</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1023,9 +1126,6 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1040,9 +1140,6 @@
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1152,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>2.580326271511701</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>7.832664507708442</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>6.973914180845489</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>11.1451154879954</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>4.696852384220176</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>9.388501149215619</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1178,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-15.16835145884005</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-13.08584996797651</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-10.29652393604015</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-13.01082724736356</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-9.043868268863319</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-9.185047350247721</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1204,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>22.3981135502236</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>41.16448753296121</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>25.6523730190528</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>40.95432174525052</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>17.36675453804046</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>28.51003595706679</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1230,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.138364925464893</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.4200112415108108</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.4490246516890338</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.7175929428234622</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.2734173646417853</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.5465318115551349</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1256,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.6486476156984688</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.5945501522713001</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.519423436886841</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.6875398914488964</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3908856785870156</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.4565322060381659</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1282,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>2.278180561281353</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>4.077240609875196</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>3.10141713215718</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>5.334860613520722</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>1.589039754868331</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2.358008464124792</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1310,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
